--- a/JsonConverter/ExcelFiles/OO_Cook.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Cook.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -42,16 +42,25 @@
       <sz val="10"/>
     </font>
     <font>
-      <name val="돋움"/>
-      <charset val="129"/>
-      <family val="3"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <family val="2"/>
-      <b val="1"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -138,27 +147,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -437,48 +443,48 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="64" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="14" customWidth="1" style="1" min="1" max="3"/>
     <col width="16" customWidth="1" style="1" min="4" max="4"/>
     <col width="14" customWidth="1" style="1" min="5" max="7"/>
-    <col width="64" customWidth="1" style="1" min="8" max="8"/>
-    <col width="64" customWidth="1" style="1" min="9" max="16384"/>
+    <col width="64" customWidth="1" style="1" min="8" max="9"/>
+    <col width="64" customWidth="1" style="1" min="10" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>완성 음식 ID</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>완성 음식 이름</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>완성 음식 설명</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>아이콘 리소스 경로</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>음식 등급</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>최대 중첩 수</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>음식 효과 설명</t>
         </is>
@@ -493,37 +499,37 @@
       <c r="O1" s="3" t="n"/>
     </row>
     <row r="2" ht="13" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -538,37 +544,37 @@
       <c r="O2" s="3" t="n"/>
     </row>
     <row r="3" ht="15.75" customFormat="1" customHeight="1" s="2">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>IconPath</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>Grade</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>MaxStackCount</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>EffectDescription</t>
         </is>
@@ -588,14 +594,14 @@
           <t>OO_VegetableSoup_1</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>채소죽</t>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>야채죽</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>쌀과 채소를 푹 끓여 만든 첫 번째 퀘스트 음식.</t>
+          <t>쌀과 채소를 넣어 끓인 따뜻한 야채죽입니다.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -613,12 +619,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>요리하기 튜토리얼 퀘스트 완료를 위해 사용한다.</t>
+          <t>첫 요리 튜토리얼 임무 완료에 사용하는 음식입니다.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>OO_GrilledFishMeal_1</t>
         </is>
@@ -631,6 +637,11 @@
       <c r="C5" t="inlineStr">
         <is>
           <t>조기를 중심으로 차린 밥상. Stage2 이후 확장용 임시 음식이다.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Images/Food/Fishbreakfast</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -641,14 +652,14 @@
       <c r="F5" t="n">
         <v>12</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Stage2에서 Stage3으로 넘어갈때 사용한다. </t>
         </is>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>OO_PumpkinSoup_1</t>
         </is>
@@ -660,7 +671,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>호박죽</t>
+          <t>호박과 쌀을 넣어 끓인 달큰한 호박죽입니다.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -678,11 +689,45 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>호박죽</t>
+          <t>Stage1 촌장 임무 완료에 사용하는 음식입니다.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15.75" customHeight="1"/>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>OO_KimchiStew_1</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>김치찌개</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>김치와 청양고추를 넣어 끓인 매운 김치찌개입니다.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Images/Food/KimchiStew</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>99</v>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>Stage2 탐욕스러운 오리에게 전달하는 퀘스트 음식입니다.</t>
+        </is>
+      </c>
+    </row>
     <row r="8" ht="15.75" customHeight="1"/>
     <row r="9" ht="15.75" customHeight="1"/>
     <row r="10" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/OO_Cook.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Cook.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="64" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="14" customWidth="1" style="1" min="1" max="3"/>
@@ -728,7 +728,41 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1"/>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>OO_KoreanCake_1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>한과</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Stage2 보상으로 받는 달콤한 전통 과자입니다. 먼 길을 가는 동료들의 기운을 북돋워 줍니다.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Images/Food/KoreanCake</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>99</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Stage2 클리어 보상으로 지급되는 음식입니다.</t>
+        </is>
+      </c>
+    </row>
     <row r="9" ht="15.75" customHeight="1"/>
     <row r="10" ht="15.75" customHeight="1"/>
     <row r="11" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/OO_Cook.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Cook.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -62,8 +62,16 @@
       <sz val="10"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="?? ??"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -95,6 +103,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE2F0D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -147,7 +160,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -165,6 +178,15 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -443,7 +465,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="64" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="14" customWidth="1" style="1" min="1" max="3"/>
@@ -729,41 +751,75 @@
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>OO_KoreanCake_1</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>한과</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Stage2 보상으로 받는 달콤한 전통 과자입니다. 먼 길을 가는 동료들의 기운을 북돋워 줍니다.</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>떡</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>절구에 쌀을 찧어 만든 쫄깃한 떡. 꿀과 합치면 산군이 좋아하는 꿀떡이 된다.</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>Images/Food/KoreanCake</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="13" t="n">
         <v>99</v>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Stage2 클리어 보상으로 지급되는 음식입니다.</t>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>Stage3 산군 퀘스트에서 꿀떡의 기본 재료로 사용한다.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1"/>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>OO_HoneyKoreanCake_1</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>꿀떡</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>떡에 꿀을 더해 만든 달콤한 꿀떡. 산군의 분노를 누그러뜨릴 수 있는 핵심 음식이다.</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>Images/Food/HoneyKoreanCake</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>좋음</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>99</v>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>Stage3 산군 퀘스트 완료에 사용하는 음식입니다.</t>
+        </is>
+      </c>
+    </row>
     <row r="10" ht="15.75" customHeight="1"/>
     <row r="11" ht="15.75" customHeight="1"/>
     <row r="12" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/OO_Cook.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Cook.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -70,8 +70,11 @@
       <name val="맑은 고딕"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -108,6 +111,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2F0D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -160,7 +178,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -186,6 +204,26 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -465,150 +503,160 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="64" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="14" customWidth="1" style="1" min="1" max="3"/>
-    <col width="16" customWidth="1" style="1" min="4" max="4"/>
-    <col width="14" customWidth="1" style="1" min="5" max="7"/>
-    <col width="64" customWidth="1" style="1" min="8" max="9"/>
-    <col width="64" customWidth="1" style="1" min="10" max="16384"/>
+    <col width="22" customWidth="1" style="1" min="1" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" style="1" min="4" max="4"/>
+    <col width="12" customWidth="1" style="1" min="5" max="7"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" style="1" min="8" max="9"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" style="1" min="10" max="16384"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>완성 음식 ID</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>완성 음식 이름</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="16" t="inlineStr">
         <is>
           <t>완성 음식 설명</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="16" t="inlineStr">
         <is>
           <t>아이콘 리소스 경로</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="16" t="inlineStr">
         <is>
           <t>음식 등급</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="16" t="inlineStr">
         <is>
           <t>최대 중첩 수</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="16" t="inlineStr">
         <is>
           <t>음식 효과 설명</t>
         </is>
       </c>
-      <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
-      <c r="O1" s="3" t="n"/>
+      <c r="H1" s="17" t="n"/>
+      <c r="I1" s="17" t="n"/>
+      <c r="J1" s="17" t="n"/>
+      <c r="K1" s="17" t="n"/>
+      <c r="L1" s="17" t="n"/>
+      <c r="M1" s="17" t="n"/>
+      <c r="N1" s="17" t="n"/>
+      <c r="O1" s="17" t="n"/>
     </row>
     <row r="2" ht="13" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="18" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="18" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="18" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="18" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="18" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="18" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="3" t="n"/>
-      <c r="K2" s="3" t="n"/>
-      <c r="L2" s="3" t="n"/>
-      <c r="M2" s="3" t="n"/>
-      <c r="N2" s="3" t="n"/>
-      <c r="O2" s="3" t="n"/>
+      <c r="H2" s="19" t="n"/>
+      <c r="I2" s="19" t="n"/>
+      <c r="J2" s="19" t="n"/>
+      <c r="K2" s="19" t="n"/>
+      <c r="L2" s="19" t="n"/>
+      <c r="M2" s="19" t="n"/>
+      <c r="N2" s="19" t="n"/>
+      <c r="O2" s="19" t="n"/>
     </row>
     <row r="3" ht="15.75" customFormat="1" customHeight="1" s="2">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="20" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="20" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="20" t="inlineStr">
         <is>
           <t>IconPath</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="20" t="inlineStr">
         <is>
           <t>Grade</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="20" t="inlineStr">
         <is>
           <t>MaxStackCount</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="20" t="inlineStr">
         <is>
           <t>EffectDescription</t>
         </is>
       </c>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="n"/>
-      <c r="K3" s="3" t="n"/>
-      <c r="L3" s="3" t="n"/>
-      <c r="M3" s="3" t="n"/>
-      <c r="N3" s="3" t="n"/>
-      <c r="O3" s="3" t="n"/>
+      <c r="H3" s="21" t="n"/>
+      <c r="I3" s="21" t="n"/>
+      <c r="J3" s="21" t="n"/>
+      <c r="K3" s="21" t="n"/>
+      <c r="L3" s="21" t="n"/>
+      <c r="M3" s="21" t="n"/>
+      <c r="N3" s="21" t="n"/>
+      <c r="O3" s="21" t="n"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" t="inlineStr">
@@ -820,9 +868,111 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="15.75" customHeight="1"/>
-    <row r="11" ht="15.75" customHeight="1"/>
-    <row r="12" ht="15.75" customHeight="1"/>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>OO_CarrotCake_1</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>당근전</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>당근전분을 가마솥에 익혀 만든 고소한 당근전입니다. 토끼를 유혹하는 Stage4 핵심 음식입니다.</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>Images/Food/CarrotCake</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>99</v>
+      </c>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>Stage4 토끼 유혹 임무에 사용하는 음식입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>OO_FinalFood_1</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>산해진미</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>마지막 무대에서 연산자군의 마음을 움직이는 상징적인 최종 요리입니다.</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>Images/Food/FinalFood</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>전설</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>99</v>
+      </c>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>FinalStage 컷신과 도감 설명용 최종 음식입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>OO_CarrotStarch_1</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>당근전분</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>당근과 떡을 섞어 만든 전분 반죽입니다. 가마솥에 익히면 당근전이 됩니다.</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>Images/Food/CarrotStarch</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>99</v>
+      </c>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>당근전을 만들기 전 단계의 조합 결과물입니다.</t>
+        </is>
+      </c>
+    </row>
     <row r="13" ht="15.75" customHeight="1"/>
     <row r="14" ht="15.75" customHeight="1"/>
     <row r="15" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/OO_Cook.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Cook.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>쌀과 채소를 넣어 끓인 따뜻한 야채죽입니다.</t>
+          <t>쌀과 채소를 넣어 끓인 따뜻한 야채죽입니다. 동쪽 마을의 굶주린 백성들을 돕는 첫 번째 요리이며, 플레이어가 조리 시스템을 익히는 시작점입니다.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>조기를 중심으로 차린 밥상. Stage2 이후 확장용 임시 음식이다.</t>
+          <t>조기를 중심으로 차린 든든한 밥상입니다. Stage2 이후 여정 확장을 위한 음식으로, 바다의 재료가 푸드카리지의 다음 가능성을 보여 줍니다.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>호박과 쌀을 넣어 끓인 달큰한 호박죽입니다.</t>
+          <t>호박과 쌀을 넣어 끓인 달큰한 호박죽입니다. 촌장 임무의 보상 교환 흐름과 연결되며, 재료를 다른 음식으로 바꾸는 구조를 알려 줍니다.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>김치와 청양고추를 넣어 끓인 매운 김치찌개입니다.</t>
+          <t>김치와 청양고추를 넣어 끓인 얼큰한 김치찌개입니다. 서쪽 도시의 탐관오리와 맞서는 과정에서 강한 맛과 결심을 상징하는 음식입니다.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>절구에 쌀을 찧어 만든 쫄깃한 떡. 꿀과 합치면 산군이 좋아하는 꿀떡이 된다.</t>
+          <t>절구에 쌀을 찧어 만든 쫄깃한 떡입니다. 꿀과 조합하면 꿀떡이 되고, 당근과 조합하면 당근전분이 되므로 Stage3 이후 핵심 재료로 계속 쓰입니다.</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>떡에 꿀을 더해 만든 달콤한 꿀떡. 산군의 분노를 누그러뜨릴 수 있는 핵심 음식이다.</t>
+          <t>떡에 꿀을 더해 만든 달콤한 꿀떡입니다. 산군의 분노를 누그러뜨리는 Stage3 핵심 음식으로, 요리가 갈등을 해결하는 장면을 보여 줍니다.</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>당근전분을 가마솥에 익혀 만든 고소한 당근전입니다. 토끼를 유혹하는 Stage4 핵심 음식입니다.</t>
+          <t>당근전분을 가마솥에 익혀 만든 고소한 당근전입니다. 토끼를 유혹하고 잠들게 하는 Stage4 핵심 음식이며, 마지막 임무 진행에 반드시 필요합니다.</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>마지막 무대에서 연산자군의 마음을 움직이는 상징적인 최종 요리입니다.</t>
+          <t>여정의 끝에서 완성되는 산해진미입니다. 모란이 지나온 모든 길과 요리의 의미를 상징하며, 최종 장면에서 이야기의 결말을 여는 음식입니다.</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>당근과 떡을 섞어 만든 전분 반죽입니다. 가마솥에 익히면 당근전이 됩니다.</t>
+          <t>떡과 당근을 조합해 만든 당근전분 반죽입니다. 그대로는 완성 음식이 아니며, 가마솥에 넣어 익혀야 토끼가 좋아하는 당근전이 됩니다.</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
